--- a/VerveStacks_BIH_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_BIH_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2750613A-BE2E-4363-A709-A16FA73CC397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4265B1C5-E4C3-47B0-98E2-9646409BA61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="106">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -277,10 +277,10 @@
     <t>BIH</t>
   </si>
   <si>
-    <t>Zenica_BIH</t>
-  </si>
-  <si>
-    <t>at grid node - Zenica_BIH</t>
+    <t>Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>at grid node - Sarajevo_BIH</t>
   </si>
   <si>
     <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
@@ -313,10 +313,16 @@
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
-    <t>Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>at grid node - Vogosca_BIH</t>
+    <t>Travnik_BIH</t>
+  </si>
+  <si>
+    <t>at grid node - Travnik_BIH</t>
+  </si>
+  <si>
+    <t>Mostar_BIH</t>
+  </si>
+  <si>
+    <t>at grid node - Mostar_BIH</t>
   </si>
   <si>
     <t>SirokiBrijeg_BIH</t>
@@ -325,12 +331,6 @@
     <t>at grid node - SirokiBrijeg_BIH</t>
   </si>
   <si>
-    <t>Mostar_BIH</t>
-  </si>
-  <si>
-    <t>at grid node - Mostar_BIH</t>
-  </si>
-  <si>
     <t>Bratunac_BIH</t>
   </si>
   <si>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>at grid node - Doboj_BIH</t>
+  </si>
+  <si>
+    <t>Orasje_BIH</t>
+  </si>
+  <si>
+    <t>at grid node - Orasje_BIH</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -677,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:Y20"/>
+  <dimension ref="B3:Y21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
@@ -809,10 +815,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O11" t="s">
         <v>99</v>
@@ -827,7 +833,7 @@
         <v>80</v>
       </c>
       <c r="T11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V11" t="s">
         <v>78</v>
@@ -839,7 +845,7 @@
         <v>80</v>
       </c>
       <c r="Y11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
@@ -871,10 +877,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O12" t="s">
         <v>99</v>
@@ -889,7 +895,7 @@
         <v>89</v>
       </c>
       <c r="T12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V12" t="s">
         <v>78</v>
@@ -901,7 +907,7 @@
         <v>89</v>
       </c>
       <c r="Y12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
@@ -971,10 +977,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O14" t="s">
         <v>99</v>
@@ -997,10 +1003,10 @@
         <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
         <v>90</v>
@@ -1009,10 +1015,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="N15" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="O15" t="s">
         <v>99</v>
@@ -1023,10 +1029,10 @@
         <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s">
         <v>90</v>
@@ -1035,10 +1041,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="N16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="O16" t="s">
         <v>99</v>
@@ -1049,10 +1055,10 @@
         <v>78</v>
       </c>
       <c r="H17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I17" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s">
         <v>90</v>
@@ -1087,10 +1093,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N18" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="O18" t="s">
         <v>99</v>
@@ -1133,6 +1139,20 @@
         <v>83</v>
       </c>
       <c r="O20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L21" t="s">
+        <v>78</v>
+      </c>
+      <c r="M21" t="s">
+        <v>84</v>
+      </c>
+      <c r="N21" t="s">
+        <v>85</v>
+      </c>
+      <c r="O21" t="s">
         <v>99</v>
       </c>
     </row>
